--- a/Teamwork.xlsx
+++ b/Teamwork.xlsx
@@ -1,34 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Documents\CSE\WebSite\cse3902web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\coeit.osu.edu\home\k\kirby.249\Documents\CSE\WebSite\cse3902web\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D631EE5B-4E61-4B06-B467-EFF2EE90FB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20964" windowHeight="3984"/>
+    <workbookView xWindow="0" yWindow="915" windowWidth="35610" windowHeight="18180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Teamwork" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="CertifiedMikuFans">Data!$A$2:$A$7</definedName>
-    <definedName name="CodeThatToad">Data!$B$2:$B$7</definedName>
-    <definedName name="FiveGuys">Data!$C$2:$C$7</definedName>
-    <definedName name="KirbySuperstars">Data!$D$2:$D$7</definedName>
-    <definedName name="MajorasMonogame">Data!$E$2:$E$7</definedName>
-    <definedName name="Thunderbird">Data!$F$2:$F$7</definedName>
+    <definedName name="DevilsDebuggers">Data!$A$2:$A$8</definedName>
+    <definedName name="Goombas">Data!$B$2:$B$8</definedName>
+    <definedName name="KirbStomp">Data!$C$2:$C$8</definedName>
+    <definedName name="MissingLink">Data!$D$2:$D$8</definedName>
+    <definedName name="SuperPlantBroz">Data!$E$2:$E$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="139">
   <si>
     <t>Team Name</t>
   </si>
@@ -330,139 +343,127 @@
     <t>An even split on a 4 person team is 15 points each.  On a 5 person team it is 12 points.  On a 6 person team it is 10 points</t>
   </si>
   <si>
-    <t>Autumn 2024</t>
-  </si>
-  <si>
-    <t>Thunderbird</t>
-  </si>
-  <si>
-    <t>KirbySuperstars</t>
-  </si>
-  <si>
-    <t>FiveGuys</t>
-  </si>
-  <si>
-    <t>MajorasMonogame</t>
-  </si>
-  <si>
-    <t>CertifiedMikuFans</t>
-  </si>
-  <si>
-    <t>CodeThatToad</t>
-  </si>
-  <si>
-    <t>Timothy Blair</t>
-  </si>
-  <si>
-    <t>Charlie Cavallaro</t>
-  </si>
-  <si>
-    <t>Noelle Lin</t>
-  </si>
-  <si>
-    <t>Wilson Lin</t>
-  </si>
-  <si>
-    <t>Vivian Qian</t>
-  </si>
-  <si>
-    <t>Songyu Ye</t>
-  </si>
-  <si>
-    <t>Joshua Han</t>
-  </si>
-  <si>
-    <t>Ekum Kaur</t>
-  </si>
-  <si>
-    <t>Ben Lampe</t>
-  </si>
-  <si>
-    <t>Bladen Siu</t>
-  </si>
-  <si>
-    <t>Tina Wang</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Christian Blue</t>
-  </si>
-  <si>
-    <t>Hahn Choi</t>
-  </si>
-  <si>
-    <t>Jingyu Fu</t>
-  </si>
-  <si>
-    <t>Zhuoyang Li</t>
-  </si>
-  <si>
-    <t>Aidan Whitlatch</t>
-  </si>
-  <si>
-    <t>Gwyneth Barnholtz</t>
-  </si>
-  <si>
-    <t>Mark DeLeo</t>
-  </si>
-  <si>
-    <t>Vivian Ferrigni</t>
-  </si>
-  <si>
-    <t>Payton Murphy</t>
-  </si>
-  <si>
-    <t>Carman Ngai</t>
-  </si>
-  <si>
-    <t>Lina Ordonez Aguiar</t>
-  </si>
-  <si>
-    <t>Solomon Blair</t>
-  </si>
-  <si>
-    <t>David Butz</t>
-  </si>
-  <si>
-    <t>Tyler Hagerman</t>
-  </si>
-  <si>
-    <t>Haopeng Liu</t>
-  </si>
-  <si>
-    <t>Nolan McCormick</t>
-  </si>
-  <si>
-    <t>Philip Simms</t>
-  </si>
-  <si>
-    <t>Brady Emmelhainz</t>
-  </si>
-  <si>
-    <t>Keaton Kinderdine</t>
-  </si>
-  <si>
-    <t>Hudson Reid</t>
-  </si>
-  <si>
-    <t>Brayden Truex</t>
-  </si>
-  <si>
-    <t>Brandon Wiedl</t>
-  </si>
-  <si>
     <t>DO NOT REORDER THE LISTS!</t>
   </si>
   <si>
     <t>USE ALL 60 POINTS!</t>
+  </si>
+  <si>
+    <t>DevilsDebuggers</t>
+  </si>
+  <si>
+    <t>Goombas</t>
+  </si>
+  <si>
+    <t>KirbStomp</t>
+  </si>
+  <si>
+    <t>MissingLink</t>
+  </si>
+  <si>
+    <t>SuperPlantBroz</t>
+  </si>
+  <si>
+    <t>Joshua A'Neal-Pack</t>
+  </si>
+  <si>
+    <t>William Blankemeyer</t>
+  </si>
+  <si>
+    <t>Gohoon Choi</t>
+  </si>
+  <si>
+    <t>Michael Hollinger</t>
+  </si>
+  <si>
+    <t>Chenzhong Li</t>
+  </si>
+  <si>
+    <t>Joshua Rhoads</t>
+  </si>
+  <si>
+    <t>Sohom Dey</t>
+  </si>
+  <si>
+    <t>Maisy Friedrichsen</t>
+  </si>
+  <si>
+    <t>Faye Leigh</t>
+  </si>
+  <si>
+    <t>Zerin Minnich</t>
+  </si>
+  <si>
+    <t>Weilun Zhou</t>
+  </si>
+  <si>
+    <t>Leo Cheng</t>
+  </si>
+  <si>
+    <t>Jed Jung</t>
+  </si>
+  <si>
+    <t>Connor Kilrain</t>
+  </si>
+  <si>
+    <t>JJ Kiratikosolrak</t>
+  </si>
+  <si>
+    <t>Colin Powers</t>
+  </si>
+  <si>
+    <t>Evan Snyder</t>
+  </si>
+  <si>
+    <t>Roi Feng</t>
+  </si>
+  <si>
+    <t>Ridwan Haque</t>
+  </si>
+  <si>
+    <t>Daniel Hensler</t>
+  </si>
+  <si>
+    <t>Jasper Li</t>
+  </si>
+  <si>
+    <t>Siddhartha Paruchuri</t>
+  </si>
+  <si>
+    <t>Zijun Zhou</t>
+  </si>
+  <si>
+    <t>Brendan Cabungcal</t>
+  </si>
+  <si>
+    <t>Peter Eberhard</t>
+  </si>
+  <si>
+    <t>Katya Liber</t>
+  </si>
+  <si>
+    <t>Ely Maddox</t>
+  </si>
+  <si>
+    <t>Brian Miller</t>
+  </si>
+  <si>
+    <t>Cameron Tucker</t>
+  </si>
+  <si>
+    <t>Andy Yu</t>
+  </si>
+  <si>
+    <t>Spring 2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1133,15 +1134,12 @@
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1196,76 +1194,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1274,6 +1202,48 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1637,56 +1607,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="64.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.33203125" customWidth="1"/>
-    <col min="9" max="10" width="27.5546875" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="64.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.28515625" customWidth="1"/>
+    <col min="9" max="10" width="27.5703125" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="77" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="4"/>
       <c r="C2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="B5" s="77" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B5" s="32" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1698,446 +1668,455 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="e">
+      <c r="A7" s="4" t="e">
         <f ca="1">INDEX(INDIRECT($B$2),ROW()-6)</f>
         <v>#REF!</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="28" t="s">
+      <c r="B7" s="33"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="34" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="e">
-        <f t="shared" ref="A8:A12" ca="1" si="0">INDEX(INDIRECT($B$2),ROW()-6)</f>
+      <c r="A8" s="4" t="e">
+        <f t="shared" ref="A8:A13" ca="1" si="0">INDEX(INDIRECT($B$2),ROW()-6)</f>
         <v>#REF!</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="28"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="34"/>
     </row>
     <row r="9" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="e">
+      <c r="A9" s="4" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="28"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="e">
+      <c r="A10" s="4" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="28"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="34"/>
     </row>
     <row r="11" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="e">
+      <c r="A11" s="4" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="28"/>
-    </row>
-    <row r="12" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="e">
+      <c r="B11" s="33"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="34"/>
+    </row>
+    <row r="12" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="28"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B12" s="33"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="34"/>
+    </row>
+    <row r="13" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="e">
+        <f t="shared" ca="1" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="34"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="27">
-        <f>SUM(B7:B12)</f>
+      <c r="B14" s="26">
+        <f>SUM(B7:B13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="7" t="str">
-        <f>IF(B13&lt;&gt;60, "MUST USE ALL 60 POINTS"," ")</f>
+      <c r="C14" s="6" t="str">
+        <f>IF(B14&lt;&gt;60, "MUST USE ALL 60 POINTS"," ")</f>
         <v>MUST USE ALL 60 POINTS</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C14" s="8" t="s">
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="C15" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H15" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
         <v>95</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J16" t="s">
         <v>96</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C16" s="25" t="s">
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="C17" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E17" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F17" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G17" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H17" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I16" s="21" t="s">
+      <c r="I17" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="21" t="s">
+      <c r="J17" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="K16" s="21" t="s">
+      <c r="K17" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="38" t="s">
+    <row r="18" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F18" s="38">
         <v>0.25</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G18" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I18" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J18" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="35" t="s">
+      <c r="K18" s="41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B18" s="23" t="s">
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="B19" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="15" t="s">
+      <c r="E19" s="45"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H19" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I19" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="J18" s="16" t="s">
+      <c r="J19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="K18" s="36"/>
-    </row>
-    <row r="19" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B19" s="24" t="s">
+      <c r="K19" s="42"/>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="B20" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C20" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="15" t="s">
+      <c r="E20" s="45"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H20" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I20" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="J19" s="16" t="s">
+      <c r="J20" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="K19" s="36"/>
-    </row>
-    <row r="20" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="K20" s="42"/>
+    </row>
+    <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="18" t="s">
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H21" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="I21" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="J20" s="19" t="s">
+      <c r="J21" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="37"/>
-    </row>
-    <row r="21" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="E21" s="38" t="s">
+      <c r="K21" s="43"/>
+    </row>
+    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="E22" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F22" s="38">
         <v>0.2</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G22" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H22" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I22" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J22" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="K21" s="35" t="s">
+      <c r="K22" s="41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E22" s="39"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="15" t="s">
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="E23" s="45"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H23" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I23" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="J22" s="16" t="s">
+      <c r="J23" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="36"/>
-    </row>
-    <row r="23" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E23" s="40"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="15" t="s">
+      <c r="K23" s="42"/>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="E24" s="46"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H24" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="I23" s="17" t="s">
+      <c r="I24" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="J24" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="K23" s="37"/>
-    </row>
-    <row r="24" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E24" s="38" t="s">
+      <c r="K24" s="43"/>
+    </row>
+    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="E25" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F25" s="38">
         <v>0.25</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G25" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H25" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I25" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J25" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="K24" s="35" t="s">
+      <c r="K25" s="41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E25" s="39"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="15" t="s">
+    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="E26" s="45"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H26" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I26" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="J25" s="16" t="s">
+      <c r="J26" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="K25" s="36"/>
-    </row>
-    <row r="26" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E26" s="39"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="15" t="s">
+      <c r="K26" s="42"/>
+    </row>
+    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="E27" s="45"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H27" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="17" t="s">
+      <c r="I27" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="J26" s="16" t="s">
+      <c r="J27" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="K26" s="36"/>
-    </row>
-    <row r="27" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E27" s="40"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="18" t="s">
+      <c r="K27" s="42"/>
+    </row>
+    <row r="28" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="E28" s="46"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H28" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I27" s="20" t="s">
+      <c r="I28" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="J27" s="19" t="s">
+      <c r="J28" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="K27" s="37"/>
-    </row>
-    <row r="28" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="E28" s="29" t="s">
+      <c r="K28" s="43"/>
+    </row>
+    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="E29" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F29" s="38">
         <v>0.3</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H29" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="14" t="s">
+      <c r="I29" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="J28" s="13" t="s">
+      <c r="J29" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="K28" s="35" t="s">
+      <c r="K29" s="41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E29" s="30"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="15" t="s">
+    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="E30" s="36"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="H30" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="I29" s="17" t="s">
+      <c r="I30" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="J29" s="16" t="s">
+      <c r="J30" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="36"/>
-    </row>
-    <row r="30" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="E30" s="30"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="15" t="s">
+      <c r="K30" s="42"/>
+    </row>
+    <row r="31" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="E31" s="36"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H31" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="I30" s="17" t="s">
+      <c r="I31" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="J30" s="16" t="s">
+      <c r="J31" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="K30" s="36"/>
-    </row>
-    <row r="31" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E31" s="30"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="15" t="s">
+      <c r="K31" s="42"/>
+    </row>
+    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="E32" s="36"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H32" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I32" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="J31" s="16" t="s">
+      <c r="J32" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="K31" s="36"/>
-    </row>
-    <row r="32" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E32" s="31"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="18" t="s">
+      <c r="K32" s="42"/>
+    </row>
+    <row r="33" spans="5:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="E33" s="37"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="H33" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I32" s="20" t="s">
+      <c r="I33" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="J32" s="19" t="s">
+      <c r="J33" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="K32" s="37"/>
+      <c r="K33" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D7:D12"/>
-    <mergeCell ref="E28:E32"/>
-    <mergeCell ref="F28:F32"/>
-    <mergeCell ref="K17:K20"/>
-    <mergeCell ref="K21:K23"/>
-    <mergeCell ref="K24:K27"/>
-    <mergeCell ref="K28:K32"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="F17:F20"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="E24:E27"/>
-    <mergeCell ref="F24:F27"/>
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="K18:K21"/>
+    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="K25:K28"/>
+    <mergeCell ref="K29:K33"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="F25:F28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A7:A12">
+  <conditionalFormatting sqref="A7:A13">
     <cfRule type="containsErrors" dxfId="4" priority="10">
       <formula>ISERROR(A7)</formula>
     </cfRule>
@@ -2147,7 +2126,7 @@
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
+  <conditionalFormatting sqref="B14">
     <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="equal">
       <formula>60</formula>
     </cfRule>
@@ -2155,16 +2134,16 @@
       <formula>60</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:C12">
+  <conditionalFormatting sqref="B7:C13">
     <cfRule type="containsBlanks" dxfId="0" priority="3">
       <formula>LEN(TRIM(B7))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Select your name" sqref="B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Select your name" sqref="B3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT(B2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($B$2)</formula1>
     </dataValidation>
   </dataValidations>
@@ -2173,13 +2152,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
-            <xm:f>Data!$A$1:$F$1</xm:f>
+            <xm:f>Data!$A$1:$E$1</xm:f>
           </x14:formula1>
           <xm:sqref>B2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>Data!$A$10:$A$13</xm:f>
           </x14:formula1>
@@ -2192,221 +2171,212 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="76" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="72" t="s">
+    <row r="1" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="D1" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="73" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" s="75" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="74" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E1" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="29"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="55" t="s">
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="D7" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="E7" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="F3" s="68" t="s">
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="25" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" s="63" t="s">
-        <v>132</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F5" s="70" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="F6" s="71" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="60" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="66" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="26" t="s">
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
